--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>48.4</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,12 +1196,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1267,39 +1263,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1444,7 +1436,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1540,7 +1532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1550,7 +1542,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1560,7 +1552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1584,7 +1576,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1598,7 +1590,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1611,7 +1603,7 @@
         <v>48.4</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1620,46 +1612,40 @@
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W4" t="n">
         <v>50</v>
       </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1804,7 +1790,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1838,56 +1824,16 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.041</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>EV helps but ISO not HR-friendly today</t>
-        </is>
-      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1900,7 +1846,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1920,12 +1866,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1944,7 +1890,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>55.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1958,7 +1904,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1971,7 +1917,7 @@
         <v>48.4</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1987,39 +1933,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2164,7 +2106,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2280,7 +2222,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2304,7 +2246,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2318,7 +2260,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2331,7 +2273,7 @@
         <v>48.4</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -2347,39 +2289,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2524,7 +2462,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2640,12 +2578,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2664,7 +2602,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2678,7 +2616,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2691,7 +2629,7 @@
         <v>48.4</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2707,39 +2645,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2884,7 +2818,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2975,24 +2909,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -3000,31 +2934,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3038,71 +2972,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
         <v>48.4</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>83</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -3119,12 +3047,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3134,12 +3062,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3149,102 +3077,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3278,56 +3206,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.424</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Elite hitter/sheet power; pitcher split less targetable</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3335,22 +3223,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3360,31 +3248,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3398,69 +3286,67 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>48.4</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>83</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3477,12 +3363,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3492,12 +3378,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3507,102 +3393,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3636,16 +3522,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Elite hitter/sheet power; pitcher split less targetable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3678,12 +3604,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3702,7 +3628,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3716,7 +3642,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3729,7 +3655,7 @@
         <v>48.4</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -3743,39 +3669,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3920,7 +3842,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3996,7 +3918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4020,7 +3942,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.8</v>
+        <v>42.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4034,7 +3956,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -4047,7 +3969,7 @@
         <v>48.4</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -4061,39 +3983,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4238,7 +4156,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4289,24 +4207,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4314,31 +4232,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4352,26 +4270,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R12" t="n">
         <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4379,42 +4297,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4431,27 +4345,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4461,102 +4375,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1853</t>
+          <t>0.1203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4607,24 +4521,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4632,31 +4546,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4670,26 +4584,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>30.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>48.4</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>50.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4697,42 +4611,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4749,27 +4659,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4779,102 +4689,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1203</t>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4925,24 +4835,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4950,31 +4860,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4988,26 +4898,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>36.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
         <v>48.4</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>35.6</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -5015,42 +4925,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -5067,12 +4973,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -5082,12 +4988,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -5097,102 +5003,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5243,24 +5149,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5268,31 +5174,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5306,26 +5212,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.3</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>48.4</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5333,42 +5239,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5385,12 +5287,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5400,12 +5302,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5415,102 +5317,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5561,24 +5463,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5586,31 +5488,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>38.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5624,26 +5526,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>48.4</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5651,42 +5553,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5703,12 +5601,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5718,12 +5616,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5733,102 +5631,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5879,24 +5777,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5904,31 +5802,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>38.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5942,26 +5840,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.4</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5969,42 +5867,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -6021,12 +5915,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -6036,12 +5930,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -6051,102 +5945,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6222,12 +6116,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6246,7 +6140,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.7</v>
+        <v>37.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6260,7 +6154,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -6273,7 +6167,7 @@
         <v>48.4</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -6287,39 +6181,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6464,7 +6354,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6540,12 +6430,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6564,7 +6454,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6578,7 +6468,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6591,7 +6481,7 @@
         <v>48.4</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -6605,39 +6495,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -6782,7 +6668,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7264,7 +7150,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7288,7 +7174,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7302,7 +7188,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7315,7 +7201,7 @@
         <v>48.4</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7331,39 +7217,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7508,7 +7390,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7624,12 +7506,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7648,7 +7530,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7662,7 +7544,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7675,7 +7557,7 @@
         <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7691,39 +7573,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7868,7 +7746,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7964,7 +7842,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7974,7 +7852,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7984,7 +7862,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -8008,7 +7886,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -8022,7 +7900,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -8035,7 +7913,7 @@
         <v>48.4</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -8044,46 +7922,40 @@
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W4" t="n">
         <v>50</v>
       </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8228,7 +8100,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8262,56 +8134,16 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.041</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>EV helps but ISO not HR-friendly today</t>
-        </is>
-      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8324,7 +8156,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8344,12 +8176,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8368,7 +8200,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>55.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8382,7 +8214,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8395,7 +8227,7 @@
         <v>48.4</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8411,39 +8243,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8588,7 +8416,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8704,7 +8532,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8728,7 +8556,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8742,7 +8570,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8755,7 +8583,7 @@
         <v>48.4</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -8771,39 +8599,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8948,7 +8772,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -9064,12 +8888,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -9088,7 +8912,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -9102,7 +8926,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -9115,7 +8939,7 @@
         <v>48.4</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -9131,39 +8955,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9308,7 +9128,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -9399,24 +9219,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9424,31 +9244,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9462,71 +9282,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
         <v>48.4</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>83</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -9543,12 +9357,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9558,12 +9372,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9573,102 +9387,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9702,56 +9516,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.424</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Elite hitter/sheet power; pitcher split less targetable</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9759,22 +9533,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9784,31 +9558,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9822,69 +9596,67 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>48.4</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>83</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -9901,12 +9673,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9916,12 +9688,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9931,102 +9703,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -10060,16 +9832,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Elite hitter/sheet power; pitcher split less targetable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10102,12 +9914,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -10126,7 +9938,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -10140,7 +9952,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -10153,7 +9965,7 @@
         <v>48.4</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -10167,39 +9979,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10344,7 +10152,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -10420,7 +10228,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10444,7 +10252,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.8</v>
+        <v>42.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -10458,7 +10266,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -10471,7 +10279,7 @@
         <v>48.4</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -10485,39 +10293,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10662,7 +10466,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10713,24 +10517,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -10738,31 +10542,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10776,26 +10580,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R12" t="n">
         <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10803,42 +10607,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10855,27 +10655,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10885,102 +10685,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1853</t>
+          <t>0.1203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -11031,24 +10831,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11056,31 +10856,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -11094,26 +10894,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>30.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>48.4</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>50.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -11121,42 +10921,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -11173,27 +10969,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -11203,102 +10999,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1203</t>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -11349,24 +11145,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11374,31 +11170,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -11412,26 +11208,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>36.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
         <v>48.4</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>35.6</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -11439,42 +11235,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -11491,12 +11283,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -11506,12 +11298,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -11521,102 +11313,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11667,24 +11459,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11692,31 +11484,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11730,26 +11522,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.3</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>48.4</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11757,42 +11549,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11809,12 +11597,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11824,12 +11612,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11839,102 +11627,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11985,24 +11773,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -12010,31 +11798,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>38.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -12048,26 +11836,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>48.4</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -12075,42 +11863,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -12127,12 +11911,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -12142,12 +11926,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -12157,102 +11941,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -12303,24 +12087,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -12328,31 +12112,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>38.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -12366,26 +12150,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.4</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -12393,42 +12177,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -12445,12 +12225,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -12460,12 +12240,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -12475,102 +12255,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12646,12 +12426,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12670,7 +12450,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.7</v>
+        <v>37.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12684,7 +12464,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -12697,7 +12477,7 @@
         <v>48.4</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -12711,39 +12491,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12888,7 +12664,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12964,12 +12740,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12988,7 +12764,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -13002,7 +12778,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -13015,7 +12791,7 @@
         <v>48.4</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -13029,39 +12805,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -13206,7 +12978,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="Q3" t="n">
         <v>21.5</v>
@@ -1209,13 +1209,13 @@
         <v>38</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>41.2</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1300,72 +1300,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>91.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0711</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4717</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.2472</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1451,24 +1451,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
         <v>38</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>41.2</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1608,112 +1608,112 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -1799,17 +1799,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.4</v>
+        <v>47.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,26 +1832,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>38</v>
       </c>
       <c r="S5" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1864,24 +1864,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1916,22 +1916,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1941,97 +1941,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.63</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0711</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4717</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2472</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>502054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Tommy Pham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.1</v>
+        <v>44.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -2163,13 +2163,13 @@
         <v>38</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>44.1</v>
+        <v>28.5</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2244,82 +2244,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>102.5676</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3666</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -2435,17 +2435,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,26 +2468,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>56.2</v>
+        <v>82</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2500,24 +2500,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2547,27 +2547,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,97 +2577,97 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
         <v>38</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>56.2</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2818,24 +2818,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -2865,27 +2865,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2895,67 +2895,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,11 +3104,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.2</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
@@ -3117,13 +3117,13 @@
         <v>38</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>77.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3183,27 +3183,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,67 +3213,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3359,24 +3359,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3389,17 +3389,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,26 +3422,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R10" t="n">
         <v>38</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3454,24 +3454,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,97 +3531,97 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3677,24 +3677,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,14 +3740,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R11" t="n">
         <v>38</v>
@@ -3756,10 +3756,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3772,24 +3772,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3819,27 +3819,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3849,97 +3849,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3995,24 +3995,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4025,17 +4025,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4058,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>10.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4090,24 +4090,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4167,97 +4167,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -4313,24 +4313,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4343,17 +4343,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4380,22 +4380,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4408,24 +4408,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4455,27 +4455,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4485,97 +4485,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
         <v>9.6</v>
@@ -4707,13 +4707,13 @@
         <v>38</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4773,22 +4773,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -4803,67 +4803,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4949,24 +4949,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4979,17 +4979,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5016,22 +5016,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>38</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5044,24 +5044,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5121,97 +5121,97 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -5343,13 +5343,13 @@
         <v>38</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5414,22 +5414,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/13, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5439,67 +5439,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.1996</t>
+          <t>99.2967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3243</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0721</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2642</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>38</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="Q3" t="n">
         <v>21.5</v>
@@ -7339,13 +7339,13 @@
         <v>38</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>41.2</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -7358,12 +7358,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7410,17 +7410,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -7430,72 +7430,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>91.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0711</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4717</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>45.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.2472</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -7581,24 +7581,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -7611,17 +7611,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7648,22 +7648,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R4" t="n">
         <v>38</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>41.2</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7676,24 +7676,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -7738,112 +7738,112 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7899,24 +7899,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -7929,17 +7929,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.4</v>
+        <v>47.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,26 +7962,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>38</v>
       </c>
       <c r="S5" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7994,24 +7994,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -8046,22 +8046,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8071,97 +8071,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>91.63</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0711</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4717</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.32</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2472</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>502054</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Tommy Pham</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.1</v>
+        <v>44.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,11 +8280,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="Q6" t="n">
         <v>21.5</v>
@@ -8293,13 +8293,13 @@
         <v>38</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>44.1</v>
+        <v>28.5</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8312,12 +8312,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8374,82 +8374,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>102.5676</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3666</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>55.52</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8535,24 +8535,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8565,17 +8565,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,26 +8598,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35.1</v>
+        <v>28.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>38</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>56.2</v>
+        <v>82</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8630,24 +8630,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8677,27 +8677,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8707,97 +8707,97 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,26 +8916,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
         <v>38</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>56.2</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8948,24 +8948,24 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -8995,27 +8995,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9025,67 +9025,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,11 +9234,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13.2</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
@@ -9247,13 +9247,13 @@
         <v>38</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>77.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9266,12 +9266,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9313,27 +9313,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9343,67 +9343,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9489,24 +9489,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9519,17 +9519,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,26 +9552,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R10" t="n">
         <v>38</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9584,24 +9584,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9631,12 +9631,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9661,97 +9661,97 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9807,24 +9807,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>38.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,14 +9870,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R11" t="n">
         <v>38</v>
@@ -9886,10 +9886,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>10.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9902,24 +9902,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9949,27 +9949,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9979,97 +9979,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -10125,24 +10125,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10155,17 +10155,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10188,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>38</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>10.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10220,24 +10220,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10297,97 +10297,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -10443,24 +10443,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10473,17 +10473,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10510,22 +10510,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R13" t="n">
         <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T13" t="n">
         <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10538,24 +10538,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10585,27 +10585,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10615,97 +10615,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10761,12 +10761,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
         <v>9.6</v>
@@ -10837,13 +10837,13 @@
         <v>38</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10856,12 +10856,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10903,22 +10903,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -10933,67 +10933,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11079,24 +11079,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -11109,17 +11109,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11146,22 +11146,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>38</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11174,24 +11174,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11251,97 +11251,97 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Luisangel Acuna</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,11 +11460,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -11473,13 +11473,13 @@
         <v>38</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11544,22 +11544,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/13, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11569,67 +11569,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.29</t>
+          <t>88.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.1996</t>
+          <t>99.2967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3243</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.0721</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2642</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -888,10 +888,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1206,10 +1202,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1524,10 +1516,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1794,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1818,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1842,10 +1830,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -1859,39 +1847,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2036,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2112,12 +2096,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,7 +2134,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2160,10 +2144,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2454,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>41.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,7 +2448,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2478,10 +2458,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2495,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2672,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,7 +2762,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2796,10 +2772,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -2990,7 +2962,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,12 +3013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3066,12 +3038,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3090,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3131,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3183,27 +3151,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,67 +3181,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3308,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3359,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3384,22 +3352,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3408,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3449,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3501,27 +3465,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,102 +3495,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3677,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3702,22 +3666,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3767,42 +3731,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3819,27 +3779,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3849,102 +3809,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3995,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4020,22 +3980,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4085,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,12 +4093,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4152,12 +4108,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4167,102 +4123,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4313,12 +4269,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4338,12 +4294,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4362,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4376,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4403,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4455,27 +4407,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4485,67 +4437,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4580,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4636,7 +4588,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4656,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4694,7 +4646,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4704,10 +4656,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4721,39 +4673,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4898,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4974,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4998,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +4960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5022,10 +4970,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -5039,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5216,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5267,24 +5211,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -5292,22 +5236,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5316,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.1</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,26 +5274,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>43.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5357,42 +5301,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5409,27 +5349,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5439,102 +5379,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5585,12 +5525,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5610,12 +5550,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5634,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5648,26 +5588,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5675,42 +5615,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5727,7 +5663,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -5737,17 +5673,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5757,84 +5693,84 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BF17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -5852,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5903,12 +5839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5928,12 +5864,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5952,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.5</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5966,26 +5902,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R18" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S18" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5993,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6045,27 +5977,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6075,67 +6007,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6170,7 +6102,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6221,12 +6153,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6246,12 +6178,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6270,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6284,26 +6216,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S19" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6311,42 +6243,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6363,27 +6291,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6393,67 +6321,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6488,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6970,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6994,7 +6922,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>57.6</v>
+        <v>56.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7008,7 +6936,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7018,10 +6946,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7035,39 +6963,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7212,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7288,12 +7212,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7312,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7326,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7336,10 +7260,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -7353,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7530,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7606,12 +7526,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7630,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7644,7 +7564,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7654,10 +7574,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -7671,39 +7591,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7848,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7924,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,7 +7878,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7972,10 +7888,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -7989,39 +7905,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8166,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8242,12 +8154,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8266,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,7 +8192,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8290,10 +8202,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -8307,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8484,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8560,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8584,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>41.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,7 +8506,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8608,10 +8516,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -8625,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8802,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8878,7 +8782,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8902,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,7 +8820,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8926,10 +8830,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -8943,39 +8847,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -9120,7 +9020,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9171,12 +9071,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9196,12 +9096,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9220,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9261,39 +9161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9313,27 +9209,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9343,67 +9239,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9438,7 +9334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9489,24 +9385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9514,22 +9410,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9538,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,26 +9448,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9579,42 +9475,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9631,27 +9523,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9661,102 +9553,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9807,24 +9699,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9832,22 +9724,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9856,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,26 +9762,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9897,42 +9789,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9949,27 +9837,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9979,102 +9867,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10125,24 +10013,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -10150,22 +10038,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10215,42 +10103,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,12 +10151,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10282,12 +10166,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10297,102 +10181,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10443,12 +10327,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10468,12 +10352,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10492,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>36.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10506,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10533,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10585,27 +10465,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10615,67 +10495,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10710,7 +10590,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10766,7 +10646,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10786,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10810,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10824,7 +10704,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10834,10 +10714,10 @@
         <v>9.6</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10851,39 +10731,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11028,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11104,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11128,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11142,7 +11018,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11152,10 +11028,10 @@
         <v>20.1</v>
       </c>
       <c r="R15" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -11169,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11346,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11397,24 +11269,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -11422,22 +11294,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11446,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.1</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,26 +11332,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>43.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11487,42 +11359,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11539,27 +11407,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11569,102 +11437,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11715,12 +11583,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11740,12 +11608,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11764,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11778,26 +11646,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11805,42 +11673,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11857,7 +11721,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -11867,17 +11731,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11887,84 +11751,84 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>98.2866</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>97.253</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.3524</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>0.1067</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>0.2943</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>69.86</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>43.71</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>25.23</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="BF17" t="inlineStr">
         <is>
           <t>0.224</t>
@@ -11982,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12033,12 +11897,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12058,12 +11922,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12082,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.5</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12096,26 +11960,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R18" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S18" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12123,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12175,27 +12035,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12205,67 +12065,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12300,7 +12160,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12351,12 +12211,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12376,12 +12236,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12400,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12414,26 +12274,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>38</v>
+        <v>27.5</v>
       </c>
       <c r="S19" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12441,42 +12301,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -12493,27 +12349,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12523,67 +12379,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12618,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>168 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>38.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>38.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1527,7 +1519,7 @@
         <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1794,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1818,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1845,7 +1833,7 @@
         <v>38.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1859,39 +1847,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2036,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2112,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,7 +2134,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2163,7 +2147,7 @@
         <v>38.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2454,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,7 +2448,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2481,7 +2461,7 @@
         <v>38.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2495,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2672,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2723,24 +2699,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -2748,22 +2724,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,26 +2762,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R8" t="n">
         <v>38.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2865,12 +2837,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2880,117 +2852,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,24 +3013,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3066,22 +3038,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3090,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.7</v>
+        <v>47</v>
       </c>
       <c r="R9" t="n">
         <v>38.6</v>
       </c>
       <c r="S9" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3131,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3183,12 +3151,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3198,117 +3166,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3384,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3408,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,7 +3390,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3435,7 +3403,7 @@
         <v>38.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3449,39 +3417,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3626,7 +3590,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3682,7 +3646,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3702,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3726,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,7 +3704,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3753,7 +3717,7 @@
         <v>38.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -3767,39 +3731,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3944,7 +3904,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3995,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4020,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4030,12 +3990,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
         <v>38.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4085,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,132 +4093,132 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4313,24 +4269,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4338,22 +4294,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4362,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4376,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
         <v>38.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4403,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4455,7 +4407,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4465,122 +4417,122 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4631,12 +4583,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4656,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4694,26 +4646,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
         <v>38.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4721,42 +4673,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4773,7 +4721,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -4783,17 +4731,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4803,67 +4751,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4898,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4974,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4998,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +4960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5025,7 +4973,7 @@
         <v>38.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -5039,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5216,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5267,24 +5211,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5292,22 +5236,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5316,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,26 +5274,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
         <v>38.6</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>43.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5357,39 +5301,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5409,132 +5349,132 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5585,12 +5525,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5610,12 +5550,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5634,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5648,11 +5588,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>47</v>
@@ -5661,13 +5601,13 @@
         <v>38.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5675,42 +5615,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5727,12 +5663,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5742,7 +5678,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5757,67 +5693,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5852,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5903,24 +5839,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5928,22 +5864,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5952,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5966,26 +5902,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
         <v>38.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5993,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6050,7 +5982,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6065,112 +5997,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6221,12 +6153,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6246,12 +6178,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6270,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6284,26 +6216,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
         <v>38.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6311,39 +6243,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6363,27 +6291,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6393,67 +6321,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6488,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6970,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6994,7 +6922,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7008,7 +6936,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7021,7 +6949,7 @@
         <v>38.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7035,39 +6963,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7212,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7288,7 +7212,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7312,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7326,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7339,7 +7263,7 @@
         <v>38.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7353,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7530,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7606,7 +7526,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7630,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7644,7 +7564,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7657,7 +7577,7 @@
         <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7671,39 +7591,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7848,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7924,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,7 +7878,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7975,7 +7891,7 @@
         <v>38.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -7989,39 +7905,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8166,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8242,7 +8154,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8266,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,7 +8192,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8293,7 +8205,7 @@
         <v>38.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -8307,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8484,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8560,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8584,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,7 +8506,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8611,7 +8519,7 @@
         <v>38.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8625,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8802,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8853,24 +8757,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -8878,22 +8782,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8902,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,26 +8820,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R8" t="n">
         <v>38.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8943,39 +8847,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8995,12 +8895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9010,117 +8910,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9171,24 +9071,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9196,22 +9096,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9220,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.7</v>
+        <v>47</v>
       </c>
       <c r="R9" t="n">
         <v>38.6</v>
       </c>
       <c r="S9" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9261,39 +9161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9313,12 +9209,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9328,117 +9224,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9514,7 +9410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9538,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,7 +9448,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9565,7 +9461,7 @@
         <v>38.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -9579,39 +9475,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -9756,7 +9648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9812,7 +9704,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9832,7 +9724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9856,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,7 +9762,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9883,7 +9775,7 @@
         <v>38.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -9897,39 +9789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10074,7 +9962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10125,24 +10013,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10150,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10160,12 +10048,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
         <v>38.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10215,42 +10103,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,132 +10151,132 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10443,24 +10327,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10468,22 +10352,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10492,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10506,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
         <v>38.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10533,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10585,7 +10465,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -10595,122 +10475,122 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10761,12 +10641,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10786,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10810,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10824,26 +10704,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
         <v>38.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10851,42 +10731,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10903,7 +10779,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -10913,17 +10789,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10933,67 +10809,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11028,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11104,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11128,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11142,7 +11018,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11155,7 +11031,7 @@
         <v>38.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -11169,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11346,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11397,24 +11269,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -11422,22 +11294,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11446,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,26 +11332,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
         <v>38.6</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>43.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11487,39 +11359,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11539,132 +11407,132 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11715,12 +11583,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11740,12 +11608,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11764,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11778,11 +11646,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>47</v>
@@ -11791,13 +11659,13 @@
         <v>38.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11805,42 +11673,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11857,12 +11721,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11872,7 +11736,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11887,67 +11751,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -11982,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12033,24 +11897,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -12058,22 +11922,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12082,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12096,26 +11960,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
         <v>38.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12123,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12180,7 +12040,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12195,112 +12055,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12351,12 +12211,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12376,12 +12236,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12400,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12414,26 +12274,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
         <v>38.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12441,39 +12301,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12493,27 +12349,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12523,67 +12379,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12618,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.3</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -888,7 +888,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>56.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>56.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.3</v>
+        <v>54.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.5</v>
+        <v>53.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>51.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.9</v>
+        <v>49.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>43.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.6</v>
+        <v>38.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6922,11 +6922,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.3</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6946,7 +6946,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>56.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>56.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.3</v>
+        <v>54.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.5</v>
+        <v>53.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>51.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.9</v>
+        <v>49.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>43.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.6</v>
+        <v>38.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3083,24 +3083,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -3113,26 +3113,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,26 +3146,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3230,22 +3230,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3255,97 +3255,97 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>41.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,11 +3464,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -3477,13 +3477,13 @@
         <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3543,22 +3543,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -3573,67 +3573,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>41.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
         <v>31.6</v>
@@ -3795,13 +3795,13 @@
         <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3861,22 +3861,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>40.4</v>
+        <v>38.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,11 +4100,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>33.4</v>
@@ -4113,13 +4113,13 @@
         <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4132,24 +4132,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -4209,67 +4209,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4418,11 +4418,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q13" t="n">
         <v>33.4</v>
@@ -4431,13 +4431,13 @@
         <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4450,24 +4450,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -4527,67 +4527,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -5309,24 +5309,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -5344,21 +5344,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>47.6</v>
@@ -5388,10 +5388,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,97 +5481,97 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>32.3</v>
+        <v>33.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -5709,7 +5709,7 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -5774,17 +5774,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5799,67 +5799,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.9</v>
+        <v>29</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,11 +6008,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -6021,13 +6021,13 @@
         <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6087,27 +6087,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,67 +6117,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.6</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6358,12 +6358,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -9255,24 +9255,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -9285,26 +9285,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,26 +9318,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>31.6</v>
       </c>
       <c r="R9" t="n">
         <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9350,12 +9350,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9402,22 +9402,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9427,97 +9427,97 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>41.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,11 +9636,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -9649,13 +9649,13 @@
         <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9668,12 +9668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -9715,22 +9715,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -9745,67 +9745,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.3</v>
+        <v>41.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
         <v>31.6</v>
@@ -9967,13 +9967,13 @@
         <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>48.7</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9986,12 +9986,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -10033,22 +10033,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -10063,67 +10063,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>40.4</v>
+        <v>38.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,11 +10272,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>33.4</v>
@@ -10285,13 +10285,13 @@
         <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10304,24 +10304,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10351,12 +10351,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -10381,67 +10381,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10590,11 +10590,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q13" t="n">
         <v>33.4</v>
@@ -10603,13 +10603,13 @@
         <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10622,24 +10622,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -10699,67 +10699,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -11481,24 +11481,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -11516,21 +11516,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11548,10 +11548,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>47.6</v>
@@ -11560,10 +11560,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,97 +11653,97 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>32.3</v>
+        <v>33.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -11881,7 +11881,7 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -11946,17 +11946,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11971,67 +11971,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.9</v>
+        <v>29</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,11 +12180,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -12193,13 +12193,13 @@
         <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -12259,27 +12259,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,67 +12289,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12484,7 +12484,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.6</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1265,39 +1261,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1442,7 +1434,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49.8</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1583,39 +1575,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.1</v>
+        <v>48.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1875,7 @@
         <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -2154,31 +2138,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,26 +2176,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
         <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,27 +2251,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2301,102 +2281,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,24 +2427,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -2472,31 +2452,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,26 +2490,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2589,12 +2565,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,12 +2580,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2619,102 +2595,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,12 +2741,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2790,12 +2766,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2814,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,11 +2804,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>21.5</v>
@@ -2841,13 +2817,13 @@
         <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2907,12 +2879,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2922,7 +2894,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -2937,67 +2909,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3032,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3060,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3118,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3131,7 @@
         <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3401,12 +3369,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3426,12 +3394,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,26 +3432,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
         <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>12</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3491,42 +3459,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3543,27 +3507,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3573,67 +3537,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3668,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,12 +3683,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3744,12 +3708,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.4</v>
+        <v>39.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,26 +3746,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
         <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>43.1</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3861,27 +3821,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,67 +3851,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3986,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +3997,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -4062,31 +4022,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.7</v>
+        <v>39.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4060,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,27 +4135,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4165,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4380,12 +4336,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.7</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4374,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R13" t="n">
         <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,42 +4401,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4497,7 +4449,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4507,17 +4459,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4622,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4673,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -4698,31 +4650,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.6</v>
+        <v>36.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R14" t="n">
         <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>38.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4763,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4815,27 +4763,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4845,102 +4793,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5016,12 +4964,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.9</v>
+        <v>33.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R15" t="n">
         <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>28.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5029,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5334,12 +5278,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,11 +5316,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -5385,13 +5329,13 @@
         <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5456,7 +5396,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,7 +5406,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -5481,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5576,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5652,12 +5592,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.6</v>
+        <v>29.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,11 +5630,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -5703,13 +5643,13 @@
         <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5769,27 +5705,27 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5894,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5970,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="R18" t="n">
         <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6092,7 +6024,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6263,12 +6195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6288,12 +6220,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="R19" t="n">
         <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6410,7 +6338,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6420,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6435,67 +6363,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6530,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -7079,39 +7007,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7256,7 +7180,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7372,7 +7296,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7396,7 +7320,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7410,7 +7334,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7423,7 +7347,7 @@
         <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7437,39 +7361,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7614,7 +7534,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>49.8</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7648,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7661,7 @@
         <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7755,39 +7675,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7932,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.1</v>
+        <v>48.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +7962,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +7975,7 @@
         <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -8326,31 +8238,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,26 +8276,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R6" t="n">
         <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,27 +8351,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8473,102 +8381,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,24 +8527,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -8644,31 +8552,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,26 +8590,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
         <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8761,12 +8665,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,12 +8680,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8791,102 +8695,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,12 +8841,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8962,12 +8866,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8986,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,11 +8904,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>21.5</v>
@@ -9013,13 +8917,13 @@
         <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9079,12 +8979,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9094,7 +8994,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -9109,67 +9009,67 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9204,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9160,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9231,7 @@
         <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9573,12 +9469,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9598,12 +9494,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,26 +9532,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R10" t="n">
         <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>12</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9663,42 +9559,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9715,27 +9607,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9745,67 +9637,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9840,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9891,12 +9783,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9916,12 +9808,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.4</v>
+        <v>39.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,26 +9846,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
         <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>43.1</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10033,27 +9921,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10063,67 +9951,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10158,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,24 +10097,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -10234,31 +10122,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.7</v>
+        <v>39.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,26 +10160,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,27 +10235,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,102 +10265,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10552,12 +10436,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.7</v>
+        <v>36.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10474,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="R13" t="n">
         <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,42 +10501,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10669,7 +10549,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -10679,17 +10559,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10794,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10845,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-14T00:00:00Z</t>
@@ -10870,31 +10750,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.6</v>
+        <v>36.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5</v>
+        <v>33.4</v>
       </c>
       <c r="R14" t="n">
         <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>38.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10935,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10987,27 +10863,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -11017,102 +10893,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11188,12 +11064,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.9</v>
+        <v>33.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="R15" t="n">
         <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>28.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11129,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11506,12 +11378,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.3</v>
+        <v>33</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,11 +11416,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q16" t="n">
         <v>21.5</v>
@@ -11557,13 +11429,13 @@
         <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11628,7 +11496,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,7 +11506,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -11653,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11748,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11824,12 +11692,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.6</v>
+        <v>29.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,11 +11730,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
         <v>21.5</v>
@@ -11875,13 +11743,13 @@
         <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11941,27 +11805,27 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12066,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12142,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="R18" t="n">
         <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12264,7 +12124,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12435,12 +12295,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12460,12 +12320,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="R19" t="n">
         <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12582,7 +12438,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12592,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12607,67 +12463,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12702,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>339 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.9</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>50.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,14 +905,14 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>5</t>
@@ -930,12 +930,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.2</v>
+        <v>54.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
@@ -1209,13 +1209,13 @@
         <v>50.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -1223,17 +1223,17 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1275,22 +1275,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1300,72 +1300,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,11 +1514,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
@@ -1527,13 +1527,13 @@
         <v>50.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1541,17 +1541,17 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1593,22 +1593,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1618,72 +1618,72 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -1845,13 +1845,13 @@
         <v>50.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1859,17 +1859,17 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1941,67 +1941,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
@@ -2163,13 +2163,13 @@
         <v>50.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2177,17 +2177,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2259,67 +2259,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,11 +2468,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
@@ -2481,13 +2481,13 @@
         <v>50.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2495,17 +2495,17 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2552,22 +2552,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,67 +2577,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,22 +3041,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,44 +3104,46 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
         <v>50.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>57</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3156,12 +3158,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3183,12 +3185,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3198,12 +3200,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3213,102 +3215,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3342,16 +3344,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3359,12 +3401,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3384,12 +3426,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3408,7 +3450,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,11 +3464,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -3435,13 +3477,13 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3459,7 +3501,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3506,22 +3548,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3531,67 +3573,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3626,7 +3668,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3677,24 +3719,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -3702,22 +3744,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3726,7 +3768,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,33 +3782,31 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>33.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T11" t="n">
+        <v>78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="V11" t="n">
         <v>50</v>
       </c>
-      <c r="U11" t="n">
-        <v>12</v>
-      </c>
-      <c r="V11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>57</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>No</t>
@@ -3779,7 +3819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3821,154 +3861,154 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/24, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>45.42</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>90.54</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>101.6393</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.4266</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.1702</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.3322</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>73.41</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>36.51</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21.26</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>83.89</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.2559</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>37.53</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>88.98</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>98.7109</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.1598</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>71.58</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.1658</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>8.65</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>37.12</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>88.27</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.3953</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.1607</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>72</t>
@@ -3980,56 +4020,16 @@
         </is>
       </c>
       <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4749,7 @@
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,14 +4763,14 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4788,12 +4788,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5067,7 +5067,7 @@
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -5081,14 +5081,14 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>8</t>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.9</v>
+        <v>58.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +7063,7 @@
         <v>50.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7077,14 +7077,14 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>5</t>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.2</v>
+        <v>54.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,11 +7368,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
@@ -7381,13 +7381,13 @@
         <v>50.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="n">
         <v>50</v>
@@ -7395,17 +7395,17 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -7447,22 +7447,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -7472,72 +7472,72 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.1</v>
+        <v>54.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7686,11 +7686,11 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
@@ -7699,13 +7699,13 @@
         <v>50.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7713,17 +7713,17 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -7790,72 +7790,72 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>51.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8004,11 +8004,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
@@ -8017,13 +8017,13 @@
         <v>50.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8031,17 +8031,17 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -8083,22 +8083,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -8113,67 +8113,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8322,11 +8322,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
@@ -8335,13 +8335,13 @@
         <v>50.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8349,17 +8349,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -8401,27 +8401,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8431,67 +8431,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8640,11 +8640,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
@@ -8653,13 +8653,13 @@
         <v>50.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8667,17 +8667,17 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -8724,22 +8724,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8749,67 +8749,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9213,22 +9213,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9276,44 +9276,46 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
         <v>50.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>57</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9328,12 +9330,12 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -9355,12 +9357,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9370,12 +9372,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9385,102 +9387,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9514,16 +9516,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9531,12 +9573,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9556,12 +9598,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9580,7 +9622,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9594,11 +9636,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -9607,13 +9649,13 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9631,7 +9673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -9678,22 +9720,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9703,67 +9745,67 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9798,7 +9840,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9849,24 +9891,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -9874,22 +9916,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9898,7 +9940,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9912,33 +9954,31 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>33.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T11" t="n">
+        <v>78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="V11" t="n">
         <v>50</v>
       </c>
-      <c r="U11" t="n">
-        <v>12</v>
-      </c>
-      <c r="V11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>57</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>No</t>
@@ -9951,7 +9991,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -9993,154 +10033,154 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/24, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>7.87</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>45.42</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>90.54</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>101.6393</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.4266</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.1702</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.3322</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>73.41</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>36.51</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>36.04</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>24.43</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21.26</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>83.89</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>0.2559</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.0609</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>37.53</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>88.98</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>98.7109</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.1598</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.3433</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>71.58</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>42.96</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.1658</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>8.65</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>37.12</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>88.27</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>0.3953</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.1607</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>72</t>
@@ -10152,56 +10192,16 @@
         </is>
       </c>
       <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10921,7 @@
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,14 +10935,14 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>9</t>
@@ -10960,12 +10960,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11239,7 +11239,7 @@
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -11253,14 +11253,14 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>8</t>
@@ -11278,12 +11278,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -910,34 +910,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1228,34 +1224,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1546,34 +1538,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1864,34 +1852,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2182,34 +2166,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2500,34 +2480,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,7 +2762,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2799,7 +2775,7 @@
         <v>50.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3138,34 +3110,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3746,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3759,7 @@
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4037,12 +3997,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4067,7 +4027,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,11 +4060,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -4113,13 +4073,13 @@
         <v>50.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,27 +4135,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,67 +4165,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4355,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4385,7 +4341,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -4431,13 +4387,13 @@
         <v>50.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4673,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4703,17 +4655,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4736,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.5</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>60.7</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4768,34 +4720,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4815,127 +4763,127 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4991,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5021,7 +4969,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5058,22 +5006,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R15" t="n">
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>60.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5086,34 +5034,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>98.7457</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5309,24 +5253,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -5344,12 +5288,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,26 +5316,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>50.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5451,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,112 +5406,112 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5627,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5657,7 +5597,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.2</v>
+        <v>29.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>50.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5769,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5945,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5975,7 +5911,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,11 +5944,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -6021,13 +5957,13 @@
         <v>50.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,42 +5971,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -6087,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,7 +6034,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6117,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6263,12 +6195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6293,7 +6225,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>50.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,42 +6285,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6405,7 +6333,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -6420,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6435,67 +6363,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -7082,34 +7010,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7400,34 +7324,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7718,34 +7638,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8036,34 +7952,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8354,34 +8266,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8672,34 +8580,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8944,7 +8848,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8958,7 +8862,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8971,7 +8875,7 @@
         <v>50.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -8985,39 +8889,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9310,34 +9210,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>50.1</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9846,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9859,7 @@
         <v>50.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10209,12 +10097,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10239,7 +10127,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,11 +10160,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -10285,13 +10173,13 @@
         <v>50.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,27 +10235,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,67 +10265,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10527,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10557,7 +10441,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.7</v>
+        <v>40.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -10603,13 +10487,13 @@
         <v>50.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10669,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10845,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -10875,17 +10755,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10908,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>37.5</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>50.1</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>60.7</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10940,34 +10820,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10987,127 +10863,127 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11163,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11193,7 +11069,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.1</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11230,22 +11106,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>37.5</v>
       </c>
       <c r="R15" t="n">
         <v>50.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>60.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11258,34 +11134,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>98.7457</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11481,24 +11353,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -11516,12 +11388,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,26 +11416,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
         <v>50.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11623,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,112 +11506,112 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -11799,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11829,7 +11697,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.2</v>
+        <v>29.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>50.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11941,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12117,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12147,7 +12011,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,11 +12044,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -12193,13 +12057,13 @@
         <v>50.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,42 +12071,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -12259,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,7 +12134,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12289,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12435,12 +12295,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12465,7 +12325,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
         <v>50.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,42 +12385,38 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -12577,7 +12433,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -12592,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12607,67 +12463,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.6</v>
+        <v>62.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -888,10 +888,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,11 +1178,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1206,10 +1202,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.6</v>
+        <v>58.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1524,10 +1516,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1769,24 +1757,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -1794,31 +1782,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,26 +1820,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1859,42 +1847,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1911,12 +1895,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1926,12 +1910,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1941,102 +1925,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2087,12 +2071,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2112,12 +2096,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.1</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,26 +2134,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2234,22 +2214,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2259,67 +2239,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2405,24 +2385,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -2430,31 +2410,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,26 +2448,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2495,42 +2475,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2547,27 +2523,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2577,102 +2553,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2723,12 +2699,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2738,7 +2714,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2748,12 +2724,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,68 +2762,62 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
         <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>100</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2867,154 +2837,154 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/26, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>37.34</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>89.87</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>98.5265</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4311</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.1567</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3363</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>69.46</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>101.2892</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.4781</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.2366</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.3565</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>78</t>
@@ -3026,56 +2996,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Dodger +19; elite sheet line vs Cameron LHH split</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3108,12 +3038,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3132,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3076,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3156,10 +3086,10 @@
         <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -3173,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3401,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3426,31 +3352,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3491,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3543,12 +3465,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3558,12 +3480,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -3573,102 +3495,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3744,31 +3666,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,42 +3731,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3861,27 +3779,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,102 +3809,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -4062,31 +3980,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4184,22 +4098,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4123,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,12 +4294,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,7 +4332,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4428,10 +4342,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -4445,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4622,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4673,22 +4583,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4698,31 +4608,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,69 +4646,67 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
-        <v>50</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57</v>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4815,175 +4723,215 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/25, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>37.53</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>88.98</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>98.7109</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.1598</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.3433</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>71.58</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>34.24</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.1658</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>UNIQLO Field at Dodger Stadium</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>43.95</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>89.29</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>100.9775</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0.4012</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>0.1674</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.3146</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>73.23</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4996,7 +4944,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5006,7 +4954,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5016,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.8</v>
+        <v>44.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,7 +5002,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5064,10 +5012,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -5076,46 +5024,40 @@
         <v>28.5</v>
       </c>
       <c r="V15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5260,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5294,56 +5236,16 @@
         </is>
       </c>
       <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
-        </is>
-      </c>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5351,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5366,7 +5268,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5376,12 +5278,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5400,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.6</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5414,68 +5316,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V16" t="n">
         <v>50</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>57</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5495,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5510,12 +5406,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5525,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5620,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5654,56 +5550,16 @@
         </is>
       </c>
       <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5711,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5736,12 +5592,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5760,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.9</v>
+        <v>37.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5774,26 +5630,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5801,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5853,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5868,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5883,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5978,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6029,12 +5881,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6054,12 +5906,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6078,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.8</v>
+        <v>37.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6092,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6119,42 +5971,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -6171,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6186,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6201,67 +6049,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6296,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6347,12 +6195,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6372,12 +6220,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6396,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6410,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6437,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6489,12 +6333,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6504,12 +6348,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6519,67 +6363,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6614,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7096,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7120,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.6</v>
+        <v>62.8</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7134,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7144,10 +6988,10 @@
         <v>39.5</v>
       </c>
       <c r="R2" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -7161,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7338,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7414,12 +7254,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7438,11 +7278,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -7452,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7462,10 +7302,10 @@
         <v>39.5</v>
       </c>
       <c r="R3" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -7479,39 +7319,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7656,7 +7492,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7732,12 +7568,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7756,7 +7592,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.6</v>
+        <v>58.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7770,7 +7606,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7780,10 +7616,10 @@
         <v>35.6</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7797,39 +7633,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7974,7 +7806,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8025,24 +7857,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8050,31 +7882,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8088,26 +7920,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R5" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8115,42 +7947,38 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -8167,12 +7995,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -8182,12 +8010,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8197,102 +8025,102 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
+          <t>0.3329</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>74.25</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>44.59</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>31.29</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>29.27</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>0.3296</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>72.62</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>26.95</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8343,12 +8171,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8368,12 +8196,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8392,7 +8220,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.1</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8406,26 +8234,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>35.6</v>
       </c>
       <c r="R6" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8433,39 +8261,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8490,22 +8314,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8515,67 +8339,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8610,7 +8434,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8661,24 +8485,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -8686,31 +8510,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.4</v>
+        <v>54.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8724,26 +8548,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>45.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R7" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8751,42 +8575,38 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8803,27 +8623,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8833,102 +8653,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8979,12 +8799,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8994,7 +8814,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9004,12 +8824,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9028,7 +8848,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9042,68 +8862,62 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55.1</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
         <v>39.5</v>
       </c>
       <c r="R8" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>100</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9123,154 +8937,154 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/26, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>37.34</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>89.87</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>98.5265</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4311</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.1567</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3363</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>69.46</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>33.31</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>90.32</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>101.2892</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.4781</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0.2366</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0.3565</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>38.7</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>78</t>
@@ -9282,56 +9096,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Dodger +19; elite sheet line vs Cameron LHH split</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9364,12 +9138,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9388,7 +9162,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9402,7 +9176,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9412,10 +9186,10 @@
         <v>35.6</v>
       </c>
       <c r="R9" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -9429,39 +9203,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9606,7 +9376,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9657,24 +9427,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -9682,31 +9452,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>49.2</v>
+        <v>51.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9720,26 +9490,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R10" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9747,42 +9517,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9799,12 +9565,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9814,12 +9580,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -9829,102 +9595,102 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9975,24 +9741,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -10000,31 +9766,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -10038,26 +9804,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.5</v>
+        <v>35.6</v>
       </c>
       <c r="R11" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -10065,42 +9831,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -10117,27 +9879,27 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10147,102 +9909,102 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10293,24 +10055,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -10318,31 +10080,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.8</v>
+        <v>51.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10356,26 +10118,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>39.5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>35.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10383,42 +10145,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10440,22 +10198,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10465,102 +10223,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10636,12 +10394,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10660,7 +10418,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10674,7 +10432,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -10684,10 +10442,10 @@
         <v>39.5</v>
       </c>
       <c r="R13" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
         <v>78</v>
@@ -10701,39 +10459,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10878,7 +10632,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10929,22 +10683,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -10954,31 +10708,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10992,69 +10746,67 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>38.2</v>
+        <v>33.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>25.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
-        <v>50</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>57</v>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -11071,175 +10823,215 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/25, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>7.72</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>37.53</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>88.98</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>98.7109</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.1598</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.3433</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>71.58</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>34.24</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.1658</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>UNIQLO Field at Dodger Stadium</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>9.81</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>43.95</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>89.29</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>100.9775</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0.4012</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>0.1674</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.3146</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>73.23</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>34.24</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>241 deg</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr"/>
-      <c r="BT14" t="inlineStr"/>
-      <c r="BU14" t="inlineStr"/>
-      <c r="BV14" t="inlineStr"/>
-      <c r="BW14" t="inlineStr"/>
-      <c r="BX14" t="inlineStr"/>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>Park/split help but hitter sheet not loud</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11252,7 +11044,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11262,7 +11054,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11272,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11296,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.8</v>
+        <v>44.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11310,7 +11102,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11320,10 +11112,10 @@
         <v>39.5</v>
       </c>
       <c r="R15" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>78</v>
@@ -11332,46 +11124,40 @@
         <v>28.5</v>
       </c>
       <c r="V15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11516,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11550,56 +11336,16 @@
         </is>
       </c>
       <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
-        </is>
-      </c>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11607,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11622,7 +11368,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11632,12 +11378,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11656,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.6</v>
+        <v>42.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11670,68 +11416,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>33.9</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
         <v>39.5</v>
       </c>
       <c r="R16" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
+        <v>78</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V16" t="n">
         <v>50</v>
       </c>
-      <c r="U16" t="n">
-        <v>12</v>
-      </c>
-      <c r="V16" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>57</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11751,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11766,12 +11506,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11781,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11876,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11910,56 +11650,16 @@
         </is>
       </c>
       <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11967,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11992,12 +11692,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -12016,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.9</v>
+        <v>37.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -12030,26 +11730,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="R17" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -12057,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -12109,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -12124,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -12139,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12234,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12285,12 +11981,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12310,12 +12006,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12334,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.8</v>
+        <v>37.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12348,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
         <v>35.6</v>
       </c>
       <c r="R18" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12375,42 +12071,38 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -12427,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12442,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12457,67 +12149,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12552,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12603,12 +12295,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12628,12 +12320,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12652,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12666,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
         <v>35.6</v>
       </c>
       <c r="R19" t="n">
-        <v>52.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12693,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12745,12 +12433,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12760,12 +12448,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12775,67 +12463,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12870,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -815,12 +815,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -845,14 +845,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.3</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -866,33 +878,31 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>48.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>37.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>No</t>
@@ -900,24 +910,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -930,7 +940,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -947,12 +957,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -962,90 +972,114 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -1082,56 +1116,16 @@
         </is>
       </c>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1139,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1154,7 +1148,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1169,14 +1163,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1194,27 +1200,29 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>37.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>48</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1222,24 +1230,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1252,7 +1260,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -1269,12 +1277,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1284,90 +1292,114 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -1404,16 +1436,56 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1421,24 +1493,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -1454,11 +1526,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1472,14 +1556,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>43.6</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R4" t="n">
         <v>37.6</v>
@@ -1488,10 +1572,10 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>54.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1504,24 +1588,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1534,7 +1618,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -1551,12 +1635,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1566,12 +1650,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1581,75 +1665,99 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -1703,12 +1811,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1733,7 +1841,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1752,7 +1860,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1766,11 +1874,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -1779,13 +1887,13 @@
         <v>37.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1798,24 +1906,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1828,7 +1936,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -1845,27 +1953,27 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1875,67 +1983,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2021,24 +2129,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2051,17 +2159,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2070,7 +2178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.7</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2084,26 +2192,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>35.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>37.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>56.2</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2116,24 +2224,24 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2146,7 +2254,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -2163,27 +2271,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2193,97 +2301,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2372,11 +2480,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>48.2</v>
+        <v>45.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2397,7 +2517,7 @@
         <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>37.6</v>
@@ -2406,7 +2526,7 @@
         <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
         <v>20.9</v>
@@ -2422,24 +2542,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2452,7 +2572,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2489,7 +2609,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2534,12 +2654,12 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2562,12 +2682,36 @@
           <t>0.1617</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -2716,7 +2860,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2833,7 +2977,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3034,7 +3178,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3287,7 +3431,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3306,7 +3450,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3333,7 +3477,7 @@
         <v>37.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3352,12 +3496,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3469,7 +3613,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3575,12 +3719,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3624,7 +3768,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3642,10 +3786,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R11" t="n">
         <v>37.6</v>
@@ -3654,10 +3798,10 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3670,24 +3814,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3700,7 +3844,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3717,7 +3861,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3727,17 +3871,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3747,67 +3891,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3893,24 +4037,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3923,17 +4067,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3942,7 +4086,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3960,22 +4104,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
         <v>37.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -3988,12 +4132,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4035,12 +4179,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4050,12 +4194,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4065,97 +4209,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -4211,24 +4355,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4241,14 +4385,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4262,26 +4418,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
         <v>37.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4294,24 +4450,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4324,7 +4480,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4341,27 +4497,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4371,75 +4527,99 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.0775</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -4493,24 +4673,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4523,14 +4703,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4544,26 +4736,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R14" t="n">
         <v>37.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4576,24 +4768,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4606,7 +4798,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4623,12 +4815,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4638,12 +4830,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4653,75 +4845,99 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -4870,7 +5086,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -5093,12 +5309,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5123,14 +5339,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5144,26 +5372,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>37.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5176,24 +5404,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5206,7 +5434,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5223,27 +5451,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5253,75 +5481,99 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -5375,12 +5627,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5405,14 +5657,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5426,26 +5690,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>37.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5458,24 +5722,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5488,7 +5752,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5505,12 +5769,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5520,12 +5784,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5535,75 +5799,99 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -5657,24 +5945,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -5687,17 +5975,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5706,7 +5994,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.9</v>
+        <v>33.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5724,22 +6012,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>37.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5752,12 +6040,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -5799,12 +6087,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5814,12 +6102,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -5829,97 +6117,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -6008,11 +6296,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>31.7</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6033,7 +6333,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>37.6</v>
@@ -6058,24 +6358,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6088,7 +6388,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6125,7 +6425,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6198,12 +6498,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -6663,12 +6987,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6678,7 +7002,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6693,14 +7017,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.3</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6714,33 +7050,31 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>48.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>37.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>No</t>
@@ -6748,24 +7082,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6778,7 +7112,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -6795,12 +7129,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -6810,90 +7144,114 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -6930,56 +7288,16 @@
         </is>
       </c>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6987,12 +7305,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7002,7 +7320,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7017,14 +7335,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7042,27 +7372,29 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>37.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>48</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7070,24 +7402,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7100,7 +7432,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -7117,12 +7449,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -7132,90 +7464,114 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -7252,16 +7608,56 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7269,24 +7665,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7302,11 +7698,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7320,14 +7728,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>43.6</v>
+        <v>53.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R4" t="n">
         <v>37.6</v>
@@ -7336,10 +7744,10 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>54.9</v>
+        <v>34.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7352,24 +7760,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7382,7 +7790,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -7399,12 +7807,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -7414,12 +7822,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -7429,75 +7837,99 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -7551,12 +7983,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7581,7 +8013,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -7600,7 +8032,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.6</v>
+        <v>48.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7614,11 +8046,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -7627,13 +8059,13 @@
         <v>37.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7646,24 +8078,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7676,7 +8108,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -7693,27 +8125,27 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -7723,67 +8155,67 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -7869,24 +8301,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7899,17 +8331,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7918,7 +8350,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.7</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7932,26 +8364,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>35.1</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>37.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>56.2</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -7964,24 +8396,24 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7994,7 +8426,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -8011,27 +8443,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8041,97 +8473,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -8220,11 +8652,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>48.2</v>
+        <v>45.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8245,7 +8689,7 @@
         <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>37.6</v>
@@ -8254,7 +8698,7 @@
         <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
         <v>20.9</v>
@@ -8270,24 +8714,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8300,7 +8744,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8337,7 +8781,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8382,12 +8826,12 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -8410,12 +8854,36 @@
           <t>0.1617</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -8564,7 +9032,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -8681,7 +9149,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -8882,7 +9350,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9135,7 +9603,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9154,7 +9622,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.1</v>
+        <v>40.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9181,7 +9649,7 @@
         <v>37.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9200,12 +9668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -9317,7 +9785,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -9423,12 +9891,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9472,7 +9940,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9490,10 +9958,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R11" t="n">
         <v>37.6</v>
@@ -9502,10 +9970,10 @@
         <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>36.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9518,24 +9986,24 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9548,7 +10016,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -9565,7 +10033,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -9575,17 +10043,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9595,67 +10063,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -9741,24 +10209,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9771,17 +10239,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9790,7 +10258,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9808,22 +10276,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
         <v>37.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -9836,12 +10304,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -9883,12 +10351,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -9898,12 +10366,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -9913,97 +10381,97 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -10059,24 +10527,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10089,14 +10557,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10110,26 +10590,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
         <v>37.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10142,24 +10622,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10172,7 +10652,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10189,27 +10669,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10219,75 +10699,99 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.0775</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -10341,24 +10845,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10371,14 +10875,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10392,26 +10908,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R14" t="n">
         <v>37.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10424,24 +10940,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10454,7 +10970,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10471,12 +10987,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -10486,12 +11002,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10501,75 +11017,99 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -10718,7 +11258,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -10941,12 +11481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10971,14 +11511,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10992,26 +11544,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>37.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11024,24 +11576,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11054,7 +11606,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11071,27 +11623,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11101,75 +11653,99 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -11223,12 +11799,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11253,14 +11829,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11274,26 +11862,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>37.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11306,24 +11894,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11336,7 +11924,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11353,12 +11941,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11368,12 +11956,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11383,75 +11971,99 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>190 deg</t>
@@ -11505,24 +12117,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -11535,17 +12147,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -11554,7 +12166,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32.9</v>
+        <v>33.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11572,22 +12184,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>37.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -11600,12 +12212,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -11647,12 +12259,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -11662,12 +12274,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -11677,97 +12289,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11856,11 +12468,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>31.7</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11881,7 +12505,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>37.6</v>
@@ -11906,24 +12530,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11936,7 +12560,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -11973,7 +12597,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12046,12 +12670,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>190 deg</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>37.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>37.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1225,39 +1221,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1402,7 +1394,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>37.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1583,39 +1575,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1875,7 @@
         <v>37.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2134,7 +2118,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2154,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2178,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,7 +2176,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2205,7 +2189,7 @@
         <v>37.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2396,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2452,7 +2432,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2472,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,7 +2490,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2523,7 +2503,7 @@
         <v>37.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2714,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2790,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2814,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,7 +2804,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2841,7 +2817,7 @@
         <v>37.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3032,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3060,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3118,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3131,7 @@
         <v>37.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,12 +3394,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.4</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>37.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,12 +3683,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3744,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,26 +3746,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
         <v>37.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,42 +3773,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -3861,7 +3821,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3871,17 +3831,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,67 +3851,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3986,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +3997,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4062,22 +4022,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.6</v>
+        <v>38.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4060,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>37.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,12 +4135,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4194,12 +4150,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4165,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,24 +4311,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4380,22 +4336,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4374,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>37.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,12 +4449,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4512,12 +4464,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,102 +4479,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4673,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4698,22 +4650,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.5</v>
+        <v>35.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>37.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4763,42 +4715,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4815,12 +4763,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4830,12 +4778,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4845,102 +4793,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5016,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,7 +5002,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5067,7 +5015,7 @@
         <v>37.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -5081,39 +5029,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5258,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5334,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,7 +5316,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5385,7 +5329,7 @@
         <v>37.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5576,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,7 +5630,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5703,7 +5643,7 @@
         <v>37.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5894,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,24 +5881,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -5970,22 +5906,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>37.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6087,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,12 +6034,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,102 +6049,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.7</v>
+        <v>30.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6339,7 +6271,7 @@
         <v>37.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6530,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>37.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7077,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7254,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,12 +7254,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7354,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7381,7 +7305,7 @@
         <v>37.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7397,39 +7321,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7574,7 +7494,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7648,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7661,7 @@
         <v>37.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7755,39 +7675,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7932,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +7962,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +7975,7 @@
         <v>37.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8306,7 +8218,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8326,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8350,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,7 +8276,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8377,7 +8289,7 @@
         <v>37.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8568,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8624,7 +8532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8644,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8668,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,7 +8590,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8695,7 +8603,7 @@
         <v>37.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8886,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8962,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8986,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,7 +8904,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -9013,7 +8917,7 @@
         <v>37.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9204,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9160,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9231,7 @@
         <v>37.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,12 +9494,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.4</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>37.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9891,12 +9783,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9916,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.2</v>
+        <v>39.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,26 +9846,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
         <v>37.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9981,42 +9873,38 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -10033,7 +9921,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -10043,17 +9931,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10063,67 +9951,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10158,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,24 +10097,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10234,22 +10122,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.6</v>
+        <v>38.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,26 +10160,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>37.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,12 +10235,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10366,12 +10250,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,102 +10265,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,24 +10411,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10552,22 +10436,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10474,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>37.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10669,12 +10549,12 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -10684,12 +10564,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,102 +10579,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10845,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10870,22 +10750,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10894,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.5</v>
+        <v>35.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>20.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>37.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10935,42 +10815,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10987,12 +10863,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -11002,12 +10878,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -11017,102 +10893,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11188,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.7</v>
+        <v>35.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,7 +11102,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11239,7 +11115,7 @@
         <v>37.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -11253,39 +11129,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11430,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11506,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,7 +11416,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -11557,7 +11429,7 @@
         <v>37.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11748,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,7 +11730,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11875,7 +11743,7 @@
         <v>37.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12066,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,24 +11981,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -12142,22 +12006,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>37.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12259,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,12 +12134,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,102 +12149,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.7</v>
+        <v>30.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -12511,7 +12371,7 @@
         <v>37.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12702,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>190 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1569,7 @@
         <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1583,39 +1583,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1760,7 +1756,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1856,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1870,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1883,7 @@
         <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1901,39 +1897,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2078,7 +2070,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,24 +2121,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2154,22 +2146,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2178,7 +2170,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,26 +2184,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2211,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,12 +2259,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2286,12 +2274,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2301,102 +2289,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,12 +2435,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2472,12 +2460,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2514,7 +2502,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -2523,13 +2511,13 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2547,7 +2535,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2589,12 +2577,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,7 +2592,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2619,67 +2607,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2714,7 +2702,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2753,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2790,22 +2778,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2828,26 +2816,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2865,7 +2853,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2907,12 +2895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2922,12 +2910,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2937,102 +2925,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3076,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3096,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3134,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3147,7 @@
         <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,7 +3410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3450,7 +3434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3448,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3461,7 @@
         <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3491,39 +3475,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3744,7 +3724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3762,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3775,7 @@
         <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3809,39 +3789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3986,7 +3962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4062,7 +4038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4086,7 +4062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,7 +4076,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -4113,7 +4089,7 @@
         <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -4127,39 +4103,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4304,7 +4276,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,7 +4352,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4622,7 +4594,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4670,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4694,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4708,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4721,7 @@
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,39 +4735,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4940,7 +4908,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,24 +4959,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5016,7 +4984,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5026,12 +4994,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5040,7 +5008,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5022,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5049,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,12 +5097,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5112,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,102 +5127,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,24 +5273,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5334,7 +5298,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5344,12 +5308,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5358,7 +5322,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,14 +5336,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>43.6</v>
@@ -5388,10 +5352,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5451,12 +5415,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5430,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,102 +5445,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,7 +5616,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5894,7 +5858,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5970,7 +5934,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6212,7 +6176,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6252,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6530,7 +6494,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,7 +6976,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7254,7 +7218,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,7 +7294,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7574,7 +7538,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7654,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7678,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7692,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7705,7 @@
         <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7755,39 +7719,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7932,7 +7892,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7968,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7992,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +8006,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +8019,7 @@
         <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8073,39 +8033,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8250,7 +8206,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,24 +8257,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8326,22 +8282,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8350,7 +8306,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,26 +8320,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8347,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,12 +8395,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8458,12 +8410,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8473,102 +8425,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,12 +8571,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8644,12 +8596,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8686,7 +8638,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -8695,13 +8647,13 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8719,7 +8671,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8761,12 +8713,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,7 +8728,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8791,67 +8743,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8886,7 +8838,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8889,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8962,22 +8914,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9000,26 +8952,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9037,7 +8989,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9079,12 +9031,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9094,12 +9046,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9109,102 +9061,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9212,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9232,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9256,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9270,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9283,7 @@
         <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9297,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9470,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,7 +9546,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9622,7 +9570,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.9</v>
+        <v>43.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9584,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9597,7 @@
         <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9663,39 +9611,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9784,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9916,7 +9860,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9884,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9898,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9911,7 @@
         <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -9981,39 +9925,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10158,7 +10098,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10234,7 +10174,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10258,7 +10198,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,7 +10212,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -10285,7 +10225,7 @@
         <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -10299,39 +10239,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10476,7 +10412,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10552,7 +10488,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10794,7 +10730,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10806,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10830,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.6</v>
+        <v>36.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10844,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10857,7 @@
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,39 +10871,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11112,7 +11044,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,24 +11095,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -11188,7 +11120,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11198,12 +11130,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11212,7 +11144,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11158,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11185,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,12 +11233,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11248,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,102 +11263,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,24 +11409,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -11506,7 +11434,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11516,12 +11444,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11530,7 +11458,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,14 +11472,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>43.6</v>
@@ -11560,10 +11488,10 @@
         <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>0.8</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11623,12 +11551,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11566,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,102 +11581,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,7 +11752,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12066,7 +11994,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12142,7 +12070,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12384,7 +12312,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12388,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12702,7 +12630,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>26 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1163,7 +1159,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1225,39 +1221,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2121,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2151,17 +2143,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2170,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2188,22 +2180,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2221,7 +2213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2259,27 +2251,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2289,97 +2281,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2440,7 +2432,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2484,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2498,7 +2490,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2511,7 +2503,7 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2525,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2753,24 +2741,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -2783,17 +2771,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2802,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2816,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2843,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2895,12 +2879,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2910,12 +2894,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2925,97 +2909,97 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -4327,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4376,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.2</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4390,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -4403,13 +4387,13 @@
         <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4417,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4469,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4499,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4645,24 +4625,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -4675,17 +4655,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4694,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4708,26 +4688,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4745,7 +4725,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4783,27 +4763,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4813,97 +4793,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4959,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4989,7 +4969,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5008,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.4</v>
+        <v>36.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5022,26 +5002,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5059,7 +5039,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -5097,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5127,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5273,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5303,7 +5283,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5322,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.9</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5336,11 +5316,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -5349,13 +5329,13 @@
         <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5363,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5415,22 +5391,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -5445,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5591,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5621,7 +5597,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5640,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5654,11 +5630,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -5667,13 +5643,13 @@
         <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5681,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5733,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5748,7 +5720,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5763,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5909,24 +5881,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -5939,17 +5911,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5958,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.2</v>
+        <v>34.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5972,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5999,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6051,27 +6019,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6081,97 +6049,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -6276,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6290,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6303,7 +6271,7 @@
         <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6317,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7000,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7014,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7027,7 +6991,7 @@
         <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7041,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7299,7 +7259,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7318,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7332,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7345,7 +7305,7 @@
         <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7361,39 +7321,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8257,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8287,17 +8243,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8306,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8324,22 +8280,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8357,7 +8313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8395,27 +8351,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8425,97 +8381,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -8576,7 +8532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8620,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8634,7 +8590,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8647,7 +8603,7 @@
         <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -8661,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8889,24 +8841,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -8919,17 +8871,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8938,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8952,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R8" t="n">
         <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8979,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9031,12 +8979,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9046,12 +8994,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9061,97 +9009,97 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -10463,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10512,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38.2</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10526,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>32</v>
@@ -10539,13 +10487,13 @@
         <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10553,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10605,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10635,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10781,24 +10725,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -10811,17 +10755,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10830,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10844,26 +10788,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
         <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>72.7</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10881,7 +10825,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10919,27 +10863,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10949,97 +10893,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11095,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11125,7 +11069,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11144,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.4</v>
+        <v>36.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11158,26 +11102,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>34.3</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>38.3</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11195,7 +11139,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -11233,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11263,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11409,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11439,7 +11383,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11458,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.9</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11472,11 +11416,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
@@ -11485,13 +11429,13 @@
         <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11499,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11551,22 +11491,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -11581,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11727,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11757,7 +11697,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11776,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>35.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11790,11 +11730,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
@@ -11803,13 +11743,13 @@
         <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11817,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11869,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11884,7 +11820,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11899,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12045,24 +11981,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-18T00:08:00Z</t>
@@ -12075,17 +12011,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12094,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33.2</v>
+        <v>34.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12108,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
         <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12135,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12187,27 +12119,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12217,97 +12149,97 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -12412,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12426,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -12439,7 +12371,7 @@
         <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12453,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2705,17 +2705,17 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3333,17 +3333,17 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3961,17 +3961,17 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4589,17 +4589,17 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4903,17 +4903,17 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.2</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6473,17 +6473,17 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7193,17 +7193,17 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.6</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S3" t="n">
         <v>94.90000000000001</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.1</v>
+        <v>50.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7863,17 +7863,17 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8177,17 +8177,17 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.3</v>
+        <v>47.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>32</v>
       </c>
       <c r="R7" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9747,17 +9747,17 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10061,17 +10061,17 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S12" t="n">
         <v>93.2</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10375,17 +10375,17 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11003,17 +11003,17 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11088,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11317,17 +11317,17 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.8</v>
+        <v>34.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11631,17 +11631,17 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11945,17 +11945,17 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.4</v>
+        <v>32.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12259,17 +12259,17 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.2</v>
+        <v>29.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>43.6</v>
+        <v>32.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -12573,17 +12573,17 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,24 +2447,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -2477,26 +2477,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,26 +2510,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2619,102 +2619,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2765,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -2795,26 +2795,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,26 +2828,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2937,102 +2937,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,24 +4037,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4067,26 +4067,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,26 +4100,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4179,27 +4179,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,102 +4209,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,24 +4355,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -4385,26 +4385,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4418,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4497,27 +4497,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,102 +4527,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,11 +5054,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
         <v>21.5</v>
@@ -5067,13 +5067,13 @@
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5086,12 +5086,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,24 +5309,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5339,26 +5339,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5376,22 +5376,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>18.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5451,27 +5451,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,102 +5481,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,24 +5627,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -5657,26 +5657,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5690,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,102 +5799,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -6021,13 +6021,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -6117,67 +6117,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.57</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,24 +8619,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8649,26 +8649,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,26 +8682,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R7" t="n">
         <v>31.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U7" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8791,102 +8791,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8937,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -8967,26 +8967,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,26 +9000,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>36.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>31.6</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>10.1</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9079,27 +9079,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9109,102 +9109,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,24 +10209,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10239,26 +10239,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.3</v>
+        <v>36.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,26 +10272,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>31.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -10351,27 +10351,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,102 +10381,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>27.96</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,24 +10527,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -10557,26 +10557,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10590,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R13" t="n">
         <v>31.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -10669,27 +10669,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,102 +10699,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>32.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,11 +11226,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7.8</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
         <v>21.5</v>
@@ -11239,13 +11239,13 @@
         <v>31.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11258,12 +11258,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11335,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,24 +11481,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11511,26 +11511,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11548,22 +11548,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
         <v>31.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>18.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11576,12 +11576,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11623,27 +11623,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,102 +11653,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,24 +11799,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-18T21:08:00Z</t>
@@ -11829,26 +11829,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11862,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>31.6</v>
       </c>
       <c r="S17" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11894,12 +11894,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,102 +11971,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
         <v>21.5</v>
@@ -12193,13 +12193,13 @@
         <v>31.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12289,67 +12289,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>211 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>31.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>78</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>31.6</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1265,39 +1261,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1442,7 +1434,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>31.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1583,